--- a/outputs/debug_canonical_smiles.xlsx
+++ b/outputs/debug_canonical_smiles.xlsx
@@ -34,22 +34,22 @@
     <t>id_type</t>
   </si>
   <si>
+    <t>CC(=O)NC1=CC=C(C=C1)O</t>
+  </si>
+  <si>
     <t>CC(=O)OC1=CC=CC=C1C(=O)O</t>
   </si>
   <si>
-    <t>CC(=O)NC1=CC=C(C=C1)O</t>
+    <t>CC(=O)Nc1ccc(O)cc1</t>
   </si>
   <si>
     <t>CC(=O)Oc1ccccc1C(=O)O</t>
   </si>
   <si>
-    <t>CC(=O)Nc1ccc(O)cc1</t>
+    <t>RZVAJINKPMORJF-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>BSYNRYMUTXBXSQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>RZVAJINKPMORJF-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>success</t>

--- a/outputs/debug_canonical_smiles.xlsx
+++ b/outputs/debug_canonical_smiles.xlsx
@@ -34,22 +34,22 @@
     <t>id_type</t>
   </si>
   <si>
+    <t>CC(=O)OC1=CC=CC=C1C(=O)O</t>
+  </si>
+  <si>
     <t>CC(=O)NC1=CC=C(C=C1)O</t>
   </si>
   <si>
-    <t>CC(=O)OC1=CC=CC=C1C(=O)O</t>
+    <t>CC(=O)Oc1ccccc1C(=O)O</t>
   </si>
   <si>
     <t>CC(=O)Nc1ccc(O)cc1</t>
   </si>
   <si>
-    <t>CC(=O)Oc1ccccc1C(=O)O</t>
+    <t>BSYNRYMUTXBXSQ-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>RZVAJINKPMORJF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>BSYNRYMUTXBXSQ-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>success</t>
